--- a/reviews/a-envoyer/le-loft-2026-09-07.xlsx
+++ b/reviews/a-envoyer/le-loft-2026-09-07.xlsx
@@ -1179,7 +1179,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-04T06:06:08</t>
+          <t>2026-09-04T09:25:01</t>
         </is>
       </c>
     </row>
